--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,6 +322,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:autorite-enregistrement</t>
   </si>
   <si>
@@ -366,9 +369,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:autorite-enregistrement.value[x]</t>
@@ -1201,24 +1201,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1243,10 +1243,10 @@
         <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1306,7 +1306,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>82</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1452,7 +1452,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1512,7 +1512,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>82</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1549,16 +1549,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1608,7 +1608,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>84</v>
@@ -1623,7 +1623,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1718,13 +1718,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1763,7 +1763,7 @@
         <v>127</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1823,7 +1823,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>82</v>
@@ -1837,7 +1837,7 @@
         <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1940,7 +1940,7 @@
         <v>129</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1969,7 +1969,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2029,7 +2029,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>82</v>
@@ -2043,7 +2043,7 @@
         <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2066,16 +2066,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2125,7 +2125,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>84</v>
@@ -2140,7 +2140,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2235,21 +2235,21 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2272,16 +2272,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2331,7 +2331,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>84</v>
@@ -2346,7 +2346,7 @@
         <v>76</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -2443,13 +2443,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
